--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -466,11 +466,7 @@
           <t>06:25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,11 +484,7 @@
           <t>14:31</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -510,11 +502,7 @@
           <t>08:16</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -532,11 +520,7 @@
           <t>10:56</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -554,11 +538,7 @@
           <t>14:11</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -576,11 +556,7 @@
           <t>17:53</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -598,11 +574,7 @@
           <t>21:34</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -620,11 +592,7 @@
           <t>00:09</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,11 +610,7 @@
           <t>19:55</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -664,11 +628,7 @@
           <t>07:10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -686,11 +646,7 @@
           <t>11:25</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -708,11 +664,7 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,11 +682,7 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -749,14 +697,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>07:34</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -771,14 +715,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -793,14 +733,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -815,14 +751,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>23:19</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -837,14 +769,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06:29</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -859,14 +787,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -881,14 +805,10 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -903,14 +823,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>21:18</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -925,14 +841,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -947,14 +859,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -969,14 +877,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>00:24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -991,14 +895,10 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1013,14 +913,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1035,14 +931,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1057,14 +949,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:39</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1079,14 +967,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:18</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1101,14 +985,10 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:20</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1123,14 +1003,10 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:50</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1145,14 +1021,10 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>00:24</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1170,11 +1042,7 @@
           <t>10:10</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1184,7 +1052,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1192,11 +1060,7 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1206,7 +1070,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1214,11 +1078,7 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1228,7 +1088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1236,11 +1096,7 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1250,7 +1106,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1258,11 +1114,7 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1272,7 +1124,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1280,11 +1132,7 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1294,7 +1142,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1302,11 +1150,7 @@
           <t>20:35</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1316,7 +1160,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1324,11 +1168,7 @@
           <t>23:35</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1338,7 +1178,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1346,11 +1186,7 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1368,11 +1204,7 @@
           <t>11:40</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1390,11 +1222,7 @@
           <t>00:40</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1409,14 +1237,10 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>07:34</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>23:19</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1431,14 +1255,10 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1453,14 +1273,10 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1475,14 +1291,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23:19</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -466,7 +466,11 @@
           <t>06:25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,7 +488,11 @@
           <t>14:31</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -502,7 +510,11 @@
           <t>08:16</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -520,7 +532,11 @@
           <t>10:56</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,7 +554,11 @@
           <t>14:11</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -556,7 +576,11 @@
           <t>17:53</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -574,7 +598,11 @@
           <t>21:34</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -592,7 +620,11 @@
           <t>00:09</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -610,7 +642,11 @@
           <t>19:55</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -628,7 +664,11 @@
           <t>07:10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -646,7 +686,11 @@
           <t>11:25</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -664,7 +708,11 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -682,7 +730,11 @@
           <t>22:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -700,7 +752,11 @@
           <t>23:19</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -718,7 +774,11 @@
           <t>07:34</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -736,7 +796,11 @@
           <t>13:01</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -754,7 +818,11 @@
           <t>17:16</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -772,7 +840,11 @@
           <t>16:59</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -790,7 +862,11 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -808,7 +884,11 @@
           <t>19:39</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -826,7 +906,11 @@
           <t>21:18</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -844,7 +928,11 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -862,7 +950,11 @@
           <t>23:50</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -880,7 +972,11 @@
           <t>00:24</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -898,7 +994,11 @@
           <t>06:29</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -916,7 +1016,11 @@
           <t>07:54</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -934,7 +1038,11 @@
           <t>09:02</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -952,7 +1060,11 @@
           <t>09:54</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -970,7 +1082,11 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -988,7 +1104,11 @@
           <t>12:45</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1006,7 +1126,11 @@
           <t>13:52</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1024,7 +1148,11 @@
           <t>14:59</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1042,7 +1170,11 @@
           <t>10:10</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1060,7 +1192,11 @@
           <t>08:30</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1078,7 +1214,11 @@
           <t>10:30</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1096,7 +1236,11 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1114,7 +1258,11 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1132,7 +1280,11 @@
           <t>18:15</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1150,7 +1302,11 @@
           <t>20:35</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1168,7 +1324,11 @@
           <t>23:35</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1186,7 +1346,11 @@
           <t>01:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1204,7 +1368,11 @@
           <t>11:40</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1222,7 +1390,11 @@
           <t>00:40</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1240,7 +1412,11 @@
           <t>23:19</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1258,7 +1434,11 @@
           <t>07:34</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1276,7 +1456,11 @@
           <t>13:01</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1294,7 +1478,11 @@
           <t>17:16</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KVC</t>
+          <t>KVC-B7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1481,6 +1481,182 @@
       <c r="D48" t="inlineStr">
         <is>
           <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -502,12 +502,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>06:29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>00:24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>8:15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8:15</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,7 +691,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>元町</t>
+          <t>元町-1W</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>元町</t>
+          <t>元町-1W</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>元町</t>
+          <t>元町-1W</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>元町</t>
+          <t>元町-1W</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -771,17 +771,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>日野</t>
+          <t>元町-9P</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>06:29</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>日野</t>
+          <t>元町-9P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -811,35 +811,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>日野</t>
+          <t>元町-9P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>日野</t>
+          <t>元町-9P</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -852,15 +856,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -870,12 +878,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -888,12 +896,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -906,12 +914,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -924,19 +932,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -946,12 +950,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -964,12 +968,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -982,12 +986,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1000,15 +1004,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:20</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1018,12 +1026,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1036,12 +1044,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>00:24</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1049,17 +1057,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>日野補給引取</t>
+          <t>日野</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1067,17 +1075,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>織機</t>
+          <t>日野</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1085,17 +1093,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>織機</t>
+          <t>日野</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1103,17 +1111,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>織機</t>
+          <t>日野</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>00:24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1121,17 +1129,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>織機</t>
+          <t>日野補給引取</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1144,12 +1152,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1162,12 +1170,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1180,12 +1188,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>23:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1198,12 +1206,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1211,17 +1219,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>額田広久手支給</t>
+          <t>織機</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1229,17 +1237,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>額田広久手支給</t>
+          <t>織機</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1247,39 +1255,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>高岡</t>
+          <t>織機</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>07:34</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>23:35</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>高岡</t>
+          <t>織機</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1287,39 +1291,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>高岡</t>
+          <t>額田広久手支給</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>高岡</t>
+          <t>額田広久手支給</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1327,35 +1327,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KVC-B3</t>
+          <t>高岡</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KVC-B3</t>
+          <t>高岡</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1363,35 +1367,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KVC-B3</t>
+          <t>高岡</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KVC-B3</t>
+          <t>高岡</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1404,12 +1412,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1422,12 +1430,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1440,12 +1448,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1458,15 +1466,87 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KVC-B3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>03</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>21:34</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/入車時間マスタ.xlsx
+++ b/入車時間マスタ.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="入車時間マスタ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入車時間マスタ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,10 +499,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,10 +521,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,7 +543,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -553,10 +561,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -571,10 +583,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:34</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -589,7 +605,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1152,7 +1168,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1170,7 +1186,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1188,7 +1204,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1206,7 +1222,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1224,7 +1240,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1242,7 +1258,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1260,7 +1276,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1278,7 +1294,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1412,15 +1428,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1430,12 +1450,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1453,7 +1473,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1471,10 +1491,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1489,10 +1513,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>21:34</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1502,12 +1530,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>00:09</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1520,12 +1548,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1538,12 +1566,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
